--- a/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
+++ b/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
@@ -97,6 +97,20 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:C2"/>
+  <dataValidations count="3">
+    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." sqref="A2:A2">
+      <formula1>2</formula1>
+      <formula2>2958465</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." sqref="B2:B2">
+      <formula1>2</formula1>
+      <formula2>2958465</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." sqref="C2:C2">
+      <formula1>2</formula1>
+      <formula2>2958465</formula2>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
 

--- a/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
+++ b/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
@@ -102,11 +102,11 @@
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." sqref="B2:B2">
+    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time." sqref="B2:B2">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." sqref="C2:C2">
+    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time." sqref="C2:C2">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
+++ b/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
@@ -98,15 +98,15 @@
   </sheetData>
   <autoFilter ref="A1:C2"/>
   <dataValidations count="3">
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." sqref="A2:A2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date.&#10;yyyy-MM-dd" prompt="Date as yyyy-MM-dd" sqref="A2:A2">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time." sqref="B2:B2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss" prompt="Date and time as yyyy-MM-dd HH:mm:ss" sqref="B2:B2">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time." sqref="C2:C2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss z" prompt="Date and time as yyyy-MM-dd HH:mm:ss z" sqref="C2:C2">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
+++ b/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
@@ -98,15 +98,15 @@
   </sheetData>
   <autoFilter ref="A1:C2"/>
   <dataValidations count="3">
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." sqref="A2:A2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date.&#10;yyyy-MM-dd" prompt="Date as yyyy-MM-dd" sqref="A2:A2">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." sqref="B2:B2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss" prompt="Date and time as yyyy-MM-dd HH:mm:ss" sqref="B2:B2">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." sqref="C2:C2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss z" prompt="Date and time as yyyy-MM-dd HH:mm:ss z" sqref="C2:C2">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
+++ b/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-01 06:30:00 +11</t>
+          <t xml:space="preserve">2020-10-01 06:30:00 +11:00</t>
         </is>
       </c>
     </row>
@@ -106,7 +106,7 @@
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss z" prompt="Date and time as yyyy-MM-dd HH:mm:ss z" sqref="C2:C2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss zzz" prompt="Date and time as yyyy-MM-dd HH:mm:ss zzz" sqref="C2:C2">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
+++ b/src/Excelsior.Tests/DateFormats.Test.verified.xlsx
@@ -115,7 +115,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1">
     <column index="1" property="DateProperty"/>
     <column index="2" property="DateTimeProperty"/>
